--- a/submission.xlsx
+++ b/submission.xlsx
@@ -46,7 +46,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Recommended for Senior AI Engineer (7.8 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) notable background at top-tier product brands, and (3) broad Jaccard skills-set overlap. Core technical alignment includes: elasticsearch, embeddings, lora, peft.</t>
+          <t>Recommended for Senior AI Engineer (7.8 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) notable background at top-tier product brands, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, embeddings, lora, peft.</t>
         </is>
       </c>
     </row>
@@ -71,7 +71,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAND_0039754</t>
+          <t>CAND_0028793</t>
         </is>
       </c>
       <c r="B4">
@@ -82,14 +82,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recommended for Senior Applied Scientist (16.2 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
+          <t>Recommended for Search Engineer (7.2 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) excellent scores on verified platform assessments, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, lora, peft, qlora.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAND_0028793</t>
+          <t>CAND_0039754</t>
         </is>
       </c>
       <c r="B5">
@@ -100,7 +100,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.2 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) excellent scores on verified platform assessments, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, lora, peft, qlora.</t>
+          <t>Recommended for Senior Applied Scientist (16.2 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -244,7 +244,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recommended for Senior Applied Scientist (5.3 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, embeddings, lora, pinecone.</t>
+          <t>Recommended for Senior Applied Scientist (5.3 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) top performance on rubric-based LLM screening, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, embeddings, lora, pinecone.</t>
         </is>
       </c>
     </row>
@@ -269,7 +269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAND_0093547</t>
+          <t>CAND_0094759</t>
         </is>
       </c>
       <c r="B15">
@@ -280,14 +280,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (2.9 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: faiss, milvus, peft, python.</t>
+          <t>Recommended for Lead AI Engineer (8.6 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) notable background at top-tier product brands, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: faiss, qdrant, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAND_0041611</t>
+          <t>CAND_0093547</t>
         </is>
       </c>
       <c r="B16">
@@ -298,14 +298,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (6.4 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) strong semantic concept alignment. Core technical alignment includes: opensearch, qdrant, qlora, weaviate.</t>
+          <t>Recommended for Senior Machine Learning Engineer (2.9 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: faiss, milvus, peft, python.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAND_0094759</t>
+          <t>CAND_0041611</t>
         </is>
       </c>
       <c r="B17">
@@ -316,7 +316,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recommended for Lead AI Engineer (8.6 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) notable background at top-tier product brands, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: faiss, qdrant, weaviate.</t>
+          <t>Recommended for Staff Machine Learning Engineer (6.4 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) strong semantic concept alignment. Core technical alignment includes: opensearch, qdrant, qlora, weaviate.</t>
         </is>
       </c>
     </row>
@@ -359,7 +359,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAND_0011687</t>
+          <t>CAND_0008425</t>
         </is>
       </c>
       <c r="B20">
@@ -370,14 +370,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, faiss, opensearch, peft.</t>
+          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: lora, python, qdrant.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAND_0068811</t>
+          <t>CAND_0011687</t>
         </is>
       </c>
       <c r="B21">
@@ -388,14 +388,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (8.0 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) strong semantic concept alignment. Core technical alignment includes: embeddings, opensearch, peft, pinecone.</t>
+          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, faiss, opensearch, peft.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CAND_0008425</t>
+          <t>CAND_0068811</t>
         </is>
       </c>
       <c r="B22">
@@ -406,7 +406,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: lora, python, qdrant.</t>
+          <t>Recommended for Applied ML Engineer (8.0 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, opensearch, peft, pinecone.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (6.5 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) broad Jaccard skills-set overlap, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, lora, peft, python.</t>
+          <t>Recommended for NLP Engineer (6.5 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) top performance on rubric-based LLM screening, and (3) broad Jaccard skills-set overlap. Core technical alignment includes: embeddings, lora, peft, python.</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (5.2 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) top performance on rubric-based LLM screening, and (3) excellent scores on verified platform assessments. Core technical alignment includes: faiss, lora, opensearch, peft.</t>
+          <t>Recommended for Search Engineer (5.2 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: faiss, lora, opensearch, peft.</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAND_0093193</t>
+          <t>CAND_0066376</t>
         </is>
       </c>
       <c r="B51">
@@ -928,14 +928,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (7.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: opensearch, qdrant.</t>
+          <t>Recommended for Applied ML Engineer (5.7 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: faiss, lora.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAND_0066376</t>
+          <t>CAND_0093193</t>
         </is>
       </c>
       <c r="B52">
@@ -946,7 +946,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (5.7 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: faiss, lora.</t>
+          <t>Recommended for Senior Machine Learning Engineer (7.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: opensearch, qdrant.</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAND_0078002</t>
+          <t>CAND_0010149</t>
         </is>
       </c>
       <c r="B55">
@@ -1000,14 +1000,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.3 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) top performance on rubric-based LLM screening. Core technical alignment includes: qlora, weaviate.</t>
+          <t>Recommended for ML Engineer (6.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, milvus, peft, qlora.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAND_0010149</t>
+          <t>CAND_0044855</t>
         </is>
       </c>
       <c r="B56">
@@ -1018,14 +1018,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Recommended for ML Engineer (6.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, milvus, peft, qlora.</t>
+          <t>Recommended for Senior Data Scientist (6.6 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) strong semantic concept alignment, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, opensearch, pinecone, qdrant.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAND_0042100</t>
+          <t>CAND_0078002</t>
         </is>
       </c>
       <c r="B57">
@@ -1036,14 +1036,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (7.3 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) comprehensive profile completeness metrics, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, pinecone, qlora.</t>
+          <t>Recommended for Machine Learning Engineer (6.3 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) top performance on rubric-based LLM screening. Core technical alignment includes: qlora, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CAND_0044855</t>
+          <t>CAND_0042100</t>
         </is>
       </c>
       <c r="B58">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (6.6 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) strong semantic concept alignment, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, opensearch, pinecone, qdrant.</t>
+          <t>Recommended for Machine Learning Engineer (7.3 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) comprehensive profile completeness metrics, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, pinecone, qlora.</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CAND_0037566</t>
+          <t>CAND_0016163</t>
         </is>
       </c>
       <c r="B61">
@@ -1108,14 +1108,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.9 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) comprehensive profile completeness metrics, and (3) excellent scores on verified platform assessments. Core technical alignment includes: elasticsearch, lora, pinecone, qlora.</t>
+          <t>Recommended for Applied ML Engineer (6.7 years of experience). Top standout factors: (1) excellent scores on verified platform assessments and (2) comprehensive profile completeness metrics. Core technical alignment includes: embeddings, lora, pinecone, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CAND_0016163</t>
+          <t>CAND_0037566</t>
         </is>
       </c>
       <c r="B62">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.7 years of experience). Top standout factors: (1) excellent scores on verified platform assessments and (2) comprehensive profile completeness metrics. Core technical alignment includes: embeddings, lora, pinecone, weaviate.</t>
+          <t>Recommended for Machine Learning Engineer (6.9 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) comprehensive profile completeness metrics, and (3) excellent scores on verified platform assessments. Core technical alignment includes: elasticsearch, lora, pinecone, qlora.</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAND_0064326</t>
+          <t>CAND_0098846</t>
         </is>
       </c>
       <c r="B66">
@@ -1198,14 +1198,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.6 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) high BM25 search relevance matching. Core technical alignment includes: milvus, python, qlora, weaviate.</t>
+          <t>Recommended for AI Engineer (7.6 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) comprehensive profile completeness metrics. Core technical alignment includes: peft, qdrant, qlora.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAND_0098846</t>
+          <t>CAND_0064326</t>
         </is>
       </c>
       <c r="B67">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (7.6 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) comprehensive profile completeness metrics. Core technical alignment includes: peft, qdrant, qlora.</t>
+          <t>Recommended for Search Engineer (7.6 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) high BM25 search relevance matching. Core technical alignment includes: milvus, python, qlora, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CAND_0055992</t>
+          <t>CAND_0052682</t>
         </is>
       </c>
       <c r="B69">
@@ -1252,14 +1252,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (16.9 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, milvus, opensearch.</t>
+          <t>Recommended for NLP Engineer (6.6 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: embeddings, faiss, python, qlora.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CAND_0052682</t>
+          <t>CAND_0066999</t>
         </is>
       </c>
       <c r="B70">
@@ -1270,14 +1270,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (6.6 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: embeddings, faiss, python, qlora.</t>
+          <t>Recommended for Recommendation Systems Engineer (5.9 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, opensearch, pinecone.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CAND_0066999</t>
+          <t>CAND_0005260</t>
         </is>
       </c>
       <c r="B71">
@@ -1288,14 +1288,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (5.9 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, opensearch, pinecone.</t>
+          <t>Recommended for Senior NLP Engineer (5.2 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, lora, python.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CAND_0005260</t>
+          <t>CAND_0040117</t>
         </is>
       </c>
       <c r="B72">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (5.2 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, lora, python.</t>
+          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, lora, qlora.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAND_0040117</t>
+          <t>CAND_0027801</t>
         </is>
       </c>
       <c r="B73">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, lora, qlora.</t>
+          <t>Recommended for NLP Engineer (7.4 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: faiss, milvus, opensearch, qlora.</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CAND_0027801</t>
+          <t>CAND_0096142</t>
         </is>
       </c>
       <c r="B75">
@@ -1360,14 +1360,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (7.4 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: faiss, milvus, opensearch, qlora.</t>
+          <t>Recommended for Applied ML Engineer (5.0 years of experience). Top standout factors: (1) excellent scores on verified platform assessments and (2) top performance on rubric-based LLM screening. Core technical alignment includes: lora, pinecone, python, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CAND_0096142</t>
+          <t>CAND_0070485</t>
         </is>
       </c>
       <c r="B76">
@@ -1378,14 +1378,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (5.0 years of experience). Top standout factors: (1) excellent scores on verified platform assessments and (2) top performance on rubric-based LLM screening. Core technical alignment includes: lora, pinecone, python, weaviate.</t>
+          <t>Recommended for Search Engineer (6.4 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: faiss, peft, qlora.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CAND_0093331</t>
+          <t>CAND_0062247</t>
         </is>
       </c>
       <c r="B77">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (16.1 years of experience). Top standout factors: (1) high recruiter interest &amp; profile visibility, (2) high BM25 search relevance matching, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: embeddings, milvus, peft, qlora.</t>
+          <t>Recommended for AI Engineer (7.3 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) comprehensive profile completeness metrics. Core technical alignment includes: peft, pinecone, qdrant.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CAND_0070485</t>
+          <t>CAND_0030468</t>
         </is>
       </c>
       <c r="B78">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (6.4 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: faiss, peft, qlora.</t>
+          <t>Recommended for Senior Applied Scientist (5.4 years of experience). Top standout factors: (1) high BM25 search relevance matching and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: milvus, opensearch.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CAND_0062247</t>
+          <t>CAND_0061655</t>
         </is>
       </c>
       <c r="B79">
@@ -1432,14 +1432,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (7.3 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) comprehensive profile completeness metrics. Core technical alignment includes: peft, pinecone, qdrant.</t>
+          <t>Recommended for Machine Learning Engineer (4.6 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) proven familiarity with adjacent technology stacks, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, opensearch, peft, pinecone.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAND_0030468</t>
+          <t>CAND_0013393</t>
         </is>
       </c>
       <c r="B80">
@@ -1450,14 +1450,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Recommended for Senior Applied Scientist (5.4 years of experience). Top standout factors: (1) high BM25 search relevance matching and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: milvus, opensearch.</t>
+          <t>Recommended for ML Engineer (5.3 years of experience). Top standout factors: (1) high recruiter interest &amp; profile visibility. Core technical alignment includes: embeddings, milvus, opensearch, pinecone.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CAND_0061655</t>
+          <t>CAND_0055992</t>
         </is>
       </c>
       <c r="B81">
@@ -1468,14 +1468,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (4.6 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) proven familiarity with adjacent technology stacks, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, opensearch, peft, pinecone.</t>
+          <t>Recommended for AI Engineer (16.9 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) high BM25 search relevance matching. Core technical alignment includes: embeddings, faiss, milvus, opensearch.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CAND_0013393</t>
+          <t>CAND_0057563</t>
         </is>
       </c>
       <c r="B82">
@@ -1486,14 +1486,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Recommended for ML Engineer (5.3 years of experience). Top standout factors: (1) high recruiter interest &amp; profile visibility. Core technical alignment includes: embeddings, milvus, opensearch, pinecone.</t>
+          <t>Recommended for NLP Engineer (6.8 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, opensearch, qlora.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CAND_0057563</t>
+          <t>CAND_0051630</t>
         </is>
       </c>
       <c r="B83">
@@ -1504,14 +1504,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (6.8 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, opensearch, qlora.</t>
+          <t>Recommended for Machine Learning Engineer (6.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CAND_0051630</t>
+          <t>CAND_0057701</t>
         </is>
       </c>
       <c r="B84">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
+          <t>Recommended for Recommendation Systems Engineer (4.1 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) strong semantic concept alignment. Core technical alignment includes: milvus, opensearch, peft, python.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAND_0057701</t>
+          <t>CAND_0064904</t>
         </is>
       </c>
       <c r="B85">
@@ -1540,14 +1540,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (4.1 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) strong semantic concept alignment. Core technical alignment includes: milvus, opensearch, peft, python.</t>
+          <t>Recommended for AI Engineer (4.9 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) broad Jaccard skills-set overlap. Core technical alignment includes: elasticsearch, embeddings, opensearch, python.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CAND_0064904</t>
+          <t>CAND_0061257</t>
         </is>
       </c>
       <c r="B86">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (4.9 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) broad Jaccard skills-set overlap. Core technical alignment includes: elasticsearch, embeddings, opensearch, python.</t>
+          <t>Recommended for Staff Machine Learning Engineer (8.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) comprehensive profile completeness metrics. Core technical alignment includes: peft, python.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CAND_0061257</t>
+          <t>CAND_0075249</t>
         </is>
       </c>
       <c r="B87">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (8.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) comprehensive profile completeness metrics. Core technical alignment includes: peft, python.</t>
+          <t>Recommended for Applied ML Engineer (6.2 years of experience). Selected based on balanced overall metrics across multiple agents. Core technical alignment includes: milvus, pinecone.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CAND_0075249</t>
+          <t>CAND_0045250</t>
         </is>
       </c>
       <c r="B89">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.2 years of experience). Selected based on balanced overall metrics across multiple agents. Core technical alignment includes: milvus, pinecone.</t>
+          <t>Recommended for Applied ML Engineer (6.6 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) broad Jaccard skills-set overlap. Core technical alignment includes: embeddings, lora, milvus, peft.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAND_0045250</t>
+          <t>CAND_0093331</t>
         </is>
       </c>
       <c r="B90">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.6 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) broad Jaccard skills-set overlap. Core technical alignment includes: embeddings, lora, milvus, peft.</t>
+          <t>Recommended for NLP Engineer (16.1 years of experience). Top standout factors: (1) high recruiter interest &amp; profile visibility, (2) high BM25 search relevance matching, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: embeddings, milvus, peft, qlora.</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CAND_0010770</t>
+          <t>CAND_0039521</t>
         </is>
       </c>
       <c r="B94">
@@ -1702,14 +1702,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (15.2 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) high BM25 search relevance matching, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: qdrant.</t>
+          <t>Recommended for Search Engineer (3.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) high BM25 search relevance matching. Core technical alignment includes: embeddings, peft, qdrant, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CAND_0039521</t>
+          <t>CAND_0075439</t>
         </is>
       </c>
       <c r="B95">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (3.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) high BM25 search relevance matching. Core technical alignment includes: embeddings, peft, qdrant, weaviate.</t>
+          <t>Recommended for Machine Learning Engineer (4.3 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CAND_0075439</t>
+          <t>CAND_0052328</t>
         </is>
       </c>
       <c r="B97">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (4.3 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
+          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: lora, opensearch, python, qlora.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CAND_0052328</t>
+          <t>CAND_0030348</t>
         </is>
       </c>
       <c r="B98">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: lora, opensearch, python, qlora.</t>
+          <t>Recommended for Machine Learning Engineer (4.5 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) top performance on rubric-based LLM screening, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, python.</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CAND_0069905</t>
+          <t>CAND_0047721</t>
         </is>
       </c>
       <c r="B100">
@@ -1810,14 +1810,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.6 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: lora, python, weaviate.</t>
+          <t>Recommended for Senior Data Scientist (7.0 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: faiss, milvus, qdrant.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CAND_0030348</t>
+          <t>CAND_0089552</t>
         </is>
       </c>
       <c r="B101">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (4.5 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) top performance on rubric-based LLM screening, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, python.</t>
+          <t>Recommended for Machine Learning Engineer (6.0 years of experience). Selected based on balanced overall metrics across multiple agents. Core technical alignment includes: milvus, qdrant, weaviate.</t>
         </is>
       </c>
     </row>

--- a/submission.xlsx
+++ b/submission.xlsx
@@ -46,7 +46,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Recommended for Senior AI Engineer (7.8 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) notable background at top-tier product brands, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, embeddings, lora, peft.</t>
+          <t>Recommended for Senior AI Engineer (7.8 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas, (2) prior experience at top-tier companies, and (3) high rating on qualifications and skills screening. Core technical alignment includes: elasticsearch, embeddings, lora, peft.</t>
         </is>
       </c>
     </row>
@@ -64,7 +64,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (8.8 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) notable background at top-tier product brands. Core technical alignment includes: elasticsearch, lora, milvus, opensearch.</t>
+          <t>Recommended for Staff Machine Learning Engineer (8.8 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) highly relevant match with job description keywords, and (3) prior experience at top-tier companies. Core technical alignment includes: elasticsearch, lora, milvus, opensearch.</t>
         </is>
       </c>
     </row>
@@ -82,7 +82,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.2 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) excellent scores on verified platform assessments, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, lora, peft, qlora.</t>
+          <t>Recommended for Search Engineer (7.2 years of experience). Top standout factors: (1) prior experience at top-tier companies, (2) excellent scores on technical skill assessments, and (3) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, lora, peft, qlora.</t>
         </is>
       </c>
     </row>
@@ -100,7 +100,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Recommended for Senior Applied Scientist (16.2 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
+          <t>Recommended for Senior Applied Scientist (16.2 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) strong matching keywords in resume text, and (3) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -118,7 +118,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Recommended for Lead AI Engineer (6.7 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) strong semantic concept alignment, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, embeddings, python, qdrant.</t>
+          <t>Recommended for Lead AI Engineer (6.7 years of experience). Top standout factors: (1) excellent profile completeness and structured details, (2) strong alignment with the core tech stack and domain, and (3) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, embeddings, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -136,7 +136,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (7.2 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, milvus, pinecone, qlora.</t>
+          <t>Recommended for Senior Machine Learning Engineer (7.2 years of experience). Top standout factors: (1) excellent profile completeness and structured details, (2) strong alignment with the core tech stack and domain, and (3) highly relevant match with job description keywords. Core technical alignment includes: embeddings, milvus, pinecone, qlora.</t>
         </is>
       </c>
     </row>
@@ -154,7 +154,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (8.9 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) strong semantic concept alignment, and (3) broad Jaccard skills-set overlap. Core technical alignment includes: elasticsearch, opensearch, peft, pinecone.</t>
+          <t>Recommended for Senior NLP Engineer (8.9 years of experience). Top standout factors: (1) prior experience at top-tier companies, (2) strong alignment with the core tech stack and domain, and (3) broad coverage of matching skills and related areas. Core technical alignment includes: elasticsearch, opensearch, peft, pinecone.</t>
         </is>
       </c>
     </row>
@@ -172,7 +172,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (8.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: elasticsearch, lora, milvus, peft.</t>
+          <t>Recommended for Senior NLP Engineer (8.0 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) strong alignment with the core tech stack and domain, and (3) highly relevant match with job description keywords. Core technical alignment includes: elasticsearch, lora, milvus, peft.</t>
         </is>
       </c>
     </row>
@@ -190,7 +190,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (8.6 years of experience). Top standout factors: (1) excellent scores on verified platform assessments, (2) top performance on rubric-based LLM screening, and (3) high BM25 search relevance matching. Core technical alignment includes: elasticsearch, lora, pinecone, python.</t>
+          <t>Recommended for Staff Machine Learning Engineer (8.6 years of experience). Top standout factors: (1) excellent scores on technical skill assessments, (2) high rating on qualifications and skills screening, and (3) highly relevant match with job description keywords. Core technical alignment includes: elasticsearch, lora, pinecone, python.</t>
         </is>
       </c>
     </row>
@@ -208,7 +208,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Recommended for Senior AI Engineer (5.9 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: faiss, opensearch, pinecone, python.</t>
+          <t>Recommended for Senior AI Engineer (5.9 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: faiss, opensearch, pinecone, python.</t>
         </is>
       </c>
     </row>
@@ -226,7 +226,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (7.0 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) high BM25 search relevance matching, and (3) comprehensive profile completeness metrics. Core technical alignment includes: opensearch, pinecone, python, qdrant.</t>
+          <t>Recommended for Staff Machine Learning Engineer (7.0 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) highly relevant match with job description keywords, and (3) excellent profile completeness and structured details. Core technical alignment includes: opensearch, pinecone, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -244,7 +244,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recommended for Senior Applied Scientist (5.3 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) top performance on rubric-based LLM screening, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, embeddings, lora, pinecone.</t>
+          <t>Recommended for Senior Applied Scientist (5.3 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) high rating on qualifications and skills screening, and (3) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, embeddings, lora, pinecone.</t>
         </is>
       </c>
     </row>
@@ -262,7 +262,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.8 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) notable background at top-tier product brands, and (3) broad Jaccard skills-set overlap. Core technical alignment includes: embeddings, peft, pinecone, python.</t>
+          <t>Recommended for Search Engineer (7.8 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas, (2) prior experience at top-tier companies, and (3) broad coverage of matching skills and related areas. Core technical alignment includes: embeddings, peft, pinecone, python.</t>
         </is>
       </c>
     </row>
@@ -280,7 +280,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Recommended for Lead AI Engineer (8.6 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) notable background at top-tier product brands, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: faiss, qdrant, weaviate.</t>
+          <t>Recommended for Lead AI Engineer (8.6 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) prior experience at top-tier companies, and (3) strong matching keywords in resume text. Core technical alignment includes: faiss, qdrant, weaviate.</t>
         </is>
       </c>
     </row>
@@ -298,7 +298,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (2.9 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: faiss, milvus, peft, python.</t>
+          <t>Recommended for Senior Machine Learning Engineer (2.9 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas, (2) strong alignment with the core tech stack and domain, and (3) highly relevant match with job description keywords. Core technical alignment includes: faiss, milvus, peft, python.</t>
         </is>
       </c>
     </row>
@@ -316,7 +316,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (6.4 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) strong semantic concept alignment. Core technical alignment includes: opensearch, qdrant, qlora, weaviate.</t>
+          <t>Recommended for Staff Machine Learning Engineer (6.4 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) strong matching keywords in resume text, and (3) strong alignment with the core tech stack and domain. Core technical alignment includes: opensearch, qdrant, qlora, weaviate.</t>
         </is>
       </c>
     </row>
@@ -334,7 +334,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (7.9 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) notable background at top-tier product brands, and (3) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, faiss, lora, opensearch.</t>
+          <t>Recommended for NLP Engineer (7.9 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) prior experience at top-tier companies, and (3) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: elasticsearch, faiss, lora, opensearch.</t>
         </is>
       </c>
     </row>
@@ -352,7 +352,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (6.1 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, qdrant.</t>
+          <t>Recommended for Senior Machine Learning Engineer (6.1 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) highly relevant match with job description keywords, and (3) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, qdrant.</t>
         </is>
       </c>
     </row>
@@ -370,7 +370,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) strong semantic concept alignment, and (3) high BM25 search relevance matching. Core technical alignment includes: lora, python, qdrant.</t>
+          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) strong alignment with the core tech stack and domain, and (3) highly relevant match with job description keywords. Core technical alignment includes: lora, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -388,7 +388,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, faiss, opensearch, peft.</t>
+          <t>Recommended for Senior NLP Engineer (7.8 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: embeddings, faiss, opensearch, peft.</t>
         </is>
       </c>
     </row>
@@ -406,7 +406,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (8.0 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, opensearch, peft, pinecone.</t>
+          <t>Recommended for Applied ML Engineer (8.0 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) proven familiarity with related tech stacks and adjacent areas, and (3) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, opensearch, peft, pinecone.</t>
         </is>
       </c>
     </row>
@@ -424,7 +424,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (6.8 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) optimal TF-IDF keyword relevance score, and (3) comprehensive profile completeness metrics. Core technical alignment includes: faiss, lora, qdrant, qlora.</t>
+          <t>Recommended for AI Engineer (6.8 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) strong matching keywords in resume text, and (3) excellent profile completeness and structured details. Core technical alignment includes: faiss, lora, qdrant, qlora.</t>
         </is>
       </c>
     </row>
@@ -442,7 +442,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (6.8 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) top performance on rubric-based LLM screening, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, milvus, peft, qlora.</t>
+          <t>Recommended for Senior NLP Engineer (6.8 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) high rating on qualifications and skills screening, and (3) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, milvus, peft, qlora.</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (6.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) strong semantic concept alignment, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: lora, opensearch, python, qlora.</t>
+          <t>Recommended for AI Engineer (6.9 years of experience). Top standout factors: (1) excellent profile completeness and structured details, (2) strong alignment with the core tech stack and domain, and (3) high rating on qualifications and skills screening. Core technical alignment includes: lora, opensearch, python, qlora.</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (5.7 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) notable background at top-tier product brands, and (3) high BM25 search relevance matching. Core technical alignment includes: lora, milvus, python, qlora.</t>
+          <t>Recommended for AI Engineer (5.7 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) prior experience at top-tier companies, and (3) highly relevant match with job description keywords. Core technical alignment includes: lora, milvus, python, qlora.</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (7.7 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: opensearch, qdrant, qlora, weaviate.</t>
+          <t>Recommended for AI Engineer (7.7 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) highly relevant match with job description keywords, and (3) high rating on qualifications and skills screening. Core technical alignment includes: opensearch, qdrant, qlora, weaviate.</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (5.1 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) broad Jaccard skills-set overlap, and (3) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, milvus, opensearch, peft.</t>
+          <t>Recommended for Applied ML Engineer (5.1 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) broad coverage of matching skills and related areas, and (3) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: elasticsearch, milvus, opensearch, peft.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (6.5 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) top performance on rubric-based LLM screening, and (3) broad Jaccard skills-set overlap. Core technical alignment includes: embeddings, lora, peft, python.</t>
+          <t>Recommended for NLP Engineer (6.5 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas, (2) high rating on qualifications and skills screening, and (3) broad coverage of matching skills and related areas. Core technical alignment includes: embeddings, lora, peft, python.</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (6.5 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) notable background at top-tier product brands, and (3) high BM25 search relevance matching. Core technical alignment includes: milvus, opensearch, python, qdrant.</t>
+          <t>Recommended for Senior Data Scientist (6.5 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) prior experience at top-tier companies, and (3) highly relevant match with job description keywords. Core technical alignment includes: milvus, opensearch, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Recommended for Senior AI Engineer (7.9 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) comprehensive profile completeness metrics, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: python.</t>
+          <t>Recommended for Senior AI Engineer (7.9 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) excellent profile completeness and structured details, and (3) strong matching keywords in resume text. Core technical alignment includes: python.</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (7.9 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, lora, opensearch, peft.</t>
+          <t>Recommended for Recommendation Systems Engineer (7.9 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) proven familiarity with related tech stacks and adjacent areas, and (3) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, lora, opensearch, peft.</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (8.0 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: opensearch, pinecone.</t>
+          <t>Recommended for Senior Machine Learning Engineer (8.0 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: opensearch, pinecone.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (5.7 years of experience). Top standout factors: (1) excellent scores on verified platform assessments, (2) optimal TF-IDF keyword relevance score, and (3) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, embeddings, opensearch, qdrant.</t>
+          <t>Recommended for Machine Learning Engineer (5.7 years of experience). Top standout factors: (1) excellent scores on technical skill assessments, (2) strong matching keywords in resume text, and (3) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: elasticsearch, embeddings, opensearch, qdrant.</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Recommended for Senior AI Engineer (5.9 years of experience). Top standout factors: (1) excellent scores on verified platform assessments, (2) comprehensive profile completeness metrics, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: lora, python, qlora.</t>
+          <t>Recommended for Senior AI Engineer (5.9 years of experience). Top standout factors: (1) excellent scores on technical skill assessments, (2) excellent profile completeness and structured details, and (3) strong matching keywords in resume text. Core technical alignment includes: lora, python, qlora.</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) strong semantic concept alignment, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: opensearch, pinecone, qdrant, qlora.</t>
+          <t>Recommended for Machine Learning Engineer (6.9 years of experience). Top standout factors: (1) excellent profile completeness and structured details, (2) strong alignment with the core tech stack and domain, and (3) high rating on qualifications and skills screening. Core technical alignment includes: opensearch, pinecone, qdrant, qlora.</t>
         </is>
       </c>
     </row>
@@ -676,14 +676,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (5.8 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, faiss, lora, milvus.</t>
+          <t>Recommended for Recommendation Systems Engineer (5.8 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) proven familiarity with related tech stacks and adjacent areas, and (3) highly relevant match with job description keywords. Core technical alignment includes: embeddings, faiss, lora, milvus.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAND_0018549</t>
+          <t>CAND_0050876</t>
         </is>
       </c>
       <c r="B38">
@@ -694,14 +694,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (6.8 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) broad Jaccard skills-set overlap, and (3) notable background at top-tier product brands. Core technical alignment includes: elasticsearch, milvus, opensearch, qdrant.</t>
+          <t>Recommended for Applied ML Engineer (6.0 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) proven familiarity with related tech stacks and adjacent areas, and (3) excellent profile completeness and structured details. Core technical alignment includes: faiss, opensearch, python, qdrant.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CAND_0050876</t>
+          <t>CAND_0018549</t>
         </is>
       </c>
       <c r="B39">
@@ -712,7 +712,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.0 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) proven familiarity with adjacent technology stacks, and (3) comprehensive profile completeness metrics. Core technical alignment includes: faiss, opensearch, python, qdrant.</t>
+          <t>Recommended for Recommendation Systems Engineer (6.8 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) broad coverage of matching skills and related areas, and (3) prior experience at top-tier companies. Core technical alignment includes: elasticsearch, milvus, opensearch, qdrant.</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (6.4 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) comprehensive profile completeness metrics. Core technical alignment includes: elasticsearch, faiss, weaviate.</t>
+          <t>Recommended for AI Engineer (6.4 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) highly relevant match with job description keywords, and (3) excellent profile completeness and structured details. Core technical alignment includes: elasticsearch, faiss, weaviate.</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (7.1 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) high BM25 search relevance matching, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, faiss, lora, qlora.</t>
+          <t>Recommended for Applied ML Engineer (7.1 years of experience). Top standout factors: (1) excellent profile completeness and structured details, (2) highly relevant match with job description keywords, and (3) high rating on qualifications and skills screening. Core technical alignment includes: elasticsearch, faiss, lora, qlora.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Recommended for Lead AI Engineer (6.4 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) comprehensive profile completeness metrics. Core technical alignment includes: elasticsearch, lora, peft, python.</t>
+          <t>Recommended for Lead AI Engineer (6.4 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) strong matching keywords in resume text, and (3) excellent profile completeness and structured details. Core technical alignment includes: elasticsearch, lora, peft, python.</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (5.3 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) notable background at top-tier product brands, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
+          <t>Recommended for Senior Data Scientist (5.3 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) prior experience at top-tier companies, and (3) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (8.0 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) top performance on rubric-based LLM screening, and (3) proven familiarity with adjacent technology stacks. Core technical alignment includes: faiss, milvus, peft, qdrant.</t>
+          <t>Recommended for Recommendation Systems Engineer (8.0 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) high rating on qualifications and skills screening, and (3) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: faiss, milvus, peft, qdrant.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (7.7 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
+          <t>Recommended for Recommendation Systems Engineer (7.7 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) proven familiarity with related tech stacks and adjacent areas, and (3) high rating on qualifications and skills screening. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (5.2 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: faiss, lora, opensearch, peft.</t>
+          <t>Recommended for Search Engineer (5.2 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) proven familiarity with related tech stacks and adjacent areas, and (3) high rating on qualifications and skills screening. Core technical alignment includes: faiss, lora, opensearch, peft.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (7.2 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) strong semantic concept alignment. Core technical alignment includes: embeddings, faiss, lora, python.</t>
+          <t>Recommended for Machine Learning Engineer (7.2 years of experience). Top standout factors: (1) excellent profile completeness and structured details and (2) strong alignment with the core tech stack and domain. Core technical alignment includes: embeddings, faiss, lora, python.</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.6 years of experience). Top standout factors: (1) strong semantic concept alignment and (2) notable background at top-tier product brands. Core technical alignment includes: elasticsearch, peft, weaviate.</t>
+          <t>Recommended for Search Engineer (7.6 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain and (2) prior experience at top-tier companies. Core technical alignment includes: elasticsearch, peft, weaviate.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (6.6 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) excellent scores on verified platform assessments, and (3) strong semantic concept alignment. Core technical alignment includes: embeddings, milvus, qdrant, qlora.</t>
+          <t>Recommended for Recommendation Systems Engineer (6.6 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) excellent scores on technical skill assessments, and (3) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: embeddings, milvus, qdrant, qlora.</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (7.4 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: faiss, lora, opensearch, weaviate.</t>
+          <t>Recommended for Applied ML Engineer (7.4 years of experience). Top standout factors: (1) high rating on qualifications and skills screening. Core technical alignment includes: faiss, lora, opensearch, weaviate.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (5.7 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: faiss, lora.</t>
+          <t>Recommended for Applied ML Engineer (5.7 years of experience). Top standout factors: (1) high rating on qualifications and skills screening and (2) strong alignment with the core tech stack and domain. Core technical alignment includes: faiss, lora.</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Recommended for Senior Machine Learning Engineer (7.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: opensearch, qdrant.</t>
+          <t>Recommended for Senior Machine Learning Engineer (7.9 years of experience). Top standout factors: (1) excellent profile completeness and structured details, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: opensearch, qdrant.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (4.9 years of experience). Top standout factors: (1) high BM25 search relevance matching, (2) optimal TF-IDF keyword relevance score, and (3) proven familiarity with adjacent technology stacks. Core technical alignment includes: embeddings, lora, milvus, opensearch.</t>
+          <t>Recommended for Recommendation Systems Engineer (4.9 years of experience). Top standout factors: (1) highly relevant match with job description keywords, (2) strong matching keywords in resume text, and (3) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: embeddings, lora, milvus, opensearch.</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (5.7 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, milvus, pinecone, qdrant.</t>
+          <t>Recommended for Staff Machine Learning Engineer (5.7 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) highly relevant match with job description keywords, and (3) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, milvus, pinecone, qdrant.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Recommended for ML Engineer (6.9 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, milvus, peft, qlora.</t>
+          <t>Recommended for ML Engineer (6.9 years of experience). Top standout factors: (1) excellent profile completeness and structured details and (2) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: elasticsearch, milvus, peft, qlora.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (6.6 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) strong semantic concept alignment, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, opensearch, pinecone, qdrant.</t>
+          <t>Recommended for Senior Data Scientist (6.6 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas, (2) strong alignment with the core tech stack and domain, and (3) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, opensearch, pinecone, qdrant.</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.3 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) top performance on rubric-based LLM screening. Core technical alignment includes: qlora, weaviate.</t>
+          <t>Recommended for Machine Learning Engineer (6.3 years of experience). Top standout factors: (1) excellent profile completeness and structured details and (2) high rating on qualifications and skills screening. Core technical alignment includes: qlora, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (7.3 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) comprehensive profile completeness metrics, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, pinecone, qlora.</t>
+          <t>Recommended for Machine Learning Engineer (7.3 years of experience). Top standout factors: (1) prior experience at top-tier companies, (2) excellent profile completeness and structured details, and (3) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, pinecone, qlora.</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.8 years of experience). Top standout factors: (1) strong semantic concept alignment and (2) high BM25 search relevance matching. Core technical alignment includes: python, qdrant, weaviate.</t>
+          <t>Recommended for Search Engineer (7.8 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain and (2) highly relevant match with job description keywords. Core technical alignment includes: python, qdrant, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (5.3 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: elasticsearch, embeddings, milvus.</t>
+          <t>Recommended for Senior Data Scientist (5.3 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: elasticsearch, embeddings, milvus.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.7 years of experience). Top standout factors: (1) excellent scores on verified platform assessments and (2) comprehensive profile completeness metrics. Core technical alignment includes: embeddings, lora, pinecone, weaviate.</t>
+          <t>Recommended for Applied ML Engineer (6.7 years of experience). Top standout factors: (1) excellent scores on technical skill assessments and (2) excellent profile completeness and structured details. Core technical alignment includes: embeddings, lora, pinecone, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.9 years of experience). Top standout factors: (1) notable background at top-tier product brands, (2) comprehensive profile completeness metrics, and (3) excellent scores on verified platform assessments. Core technical alignment includes: elasticsearch, lora, pinecone, qlora.</t>
+          <t>Recommended for Machine Learning Engineer (6.9 years of experience). Top standout factors: (1) prior experience at top-tier companies, (2) excellent profile completeness and structured details, and (3) excellent scores on technical skill assessments. Core technical alignment includes: elasticsearch, lora, pinecone, qlora.</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (4.8 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap, (2) proven familiarity with adjacent technology stacks, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, lora, milvus.</t>
+          <t>Recommended for Recommendation Systems Engineer (4.8 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas, (2) proven familiarity with related tech stacks and adjacent areas, and (3) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, faiss, lora, milvus.</t>
         </is>
       </c>
     </row>
@@ -1180,14 +1180,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (5.4 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks, (2) excellent scores on verified platform assessments, and (3) top performance on rubric-based LLM screening. Core technical alignment includes: lora, opensearch, qdrant, qlora.</t>
+          <t>Recommended for NLP Engineer (5.4 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas, (2) excellent scores on technical skill assessments, and (3) high rating on qualifications and skills screening. Core technical alignment includes: lora, opensearch, qdrant, qlora.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CAND_0098846</t>
+          <t>CAND_0064326</t>
         </is>
       </c>
       <c r="B66">
@@ -1198,14 +1198,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (7.6 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) comprehensive profile completeness metrics. Core technical alignment includes: peft, qdrant, qlora.</t>
+          <t>Recommended for Search Engineer (7.6 years of experience). Top standout factors: (1) excellent profile completeness and structured details and (2) highly relevant match with job description keywords. Core technical alignment includes: milvus, python, qlora, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CAND_0064326</t>
+          <t>CAND_0098846</t>
         </is>
       </c>
       <c r="B67">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (7.6 years of experience). Top standout factors: (1) comprehensive profile completeness metrics and (2) high BM25 search relevance matching. Core technical alignment includes: milvus, python, qlora, weaviate.</t>
+          <t>Recommended for AI Engineer (7.6 years of experience). Top standout factors: (1) prior experience at top-tier companies and (2) excellent profile completeness and structured details. Core technical alignment includes: peft, qdrant, qlora.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (7.4 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening, (2) high BM25 search relevance matching, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: qlora, weaviate.</t>
+          <t>Recommended for Senior Data Scientist (7.4 years of experience). Top standout factors: (1) high rating on qualifications and skills screening, (2) highly relevant match with job description keywords, and (3) strong matching keywords in resume text. Core technical alignment includes: qlora, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (6.6 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: embeddings, faiss, python, qlora.</t>
+          <t>Recommended for NLP Engineer (6.6 years of experience). Top standout factors: (1) high rating on qualifications and skills screening and (2) strong alignment with the core tech stack and domain. Core technical alignment includes: embeddings, faiss, python, qlora.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (5.9 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, opensearch, pinecone.</t>
+          <t>Recommended for Recommendation Systems Engineer (5.9 years of experience). Top standout factors: (1) prior experience at top-tier companies and (2) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, faiss, opensearch, pinecone.</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Recommended for Senior NLP Engineer (5.2 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: embeddings, lora, python.</t>
+          <t>Recommended for Senior NLP Engineer (5.2 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: embeddings, lora, python.</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: embeddings, faiss, lora, qlora.</t>
+          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) high rating on qualifications and skills screening. Core technical alignment includes: embeddings, faiss, lora, qlora.</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (7.4 years of experience). Top standout factors: (1) notable background at top-tier product brands and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: faiss, milvus, opensearch, qlora.</t>
+          <t>Recommended for NLP Engineer (7.4 years of experience). Top standout factors: (1) prior experience at top-tier companies and (2) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: faiss, milvus, opensearch, qlora.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (5.0 years of experience). Top standout factors: (1) excellent scores on verified platform assessments and (2) top performance on rubric-based LLM screening. Core technical alignment includes: lora, pinecone, python, weaviate.</t>
+          <t>Recommended for Applied ML Engineer (5.0 years of experience). Top standout factors: (1) excellent scores on technical skill assessments and (2) high rating on qualifications and skills screening. Core technical alignment includes: lora, pinecone, python, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (6.4 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: faiss, peft, qlora.</t>
+          <t>Recommended for Search Engineer (6.4 years of experience). Top standout factors: (1) high rating on qualifications and skills screening and (2) strong matching keywords in resume text. Core technical alignment includes: faiss, peft, qlora.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (7.3 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) comprehensive profile completeness metrics. Core technical alignment includes: peft, pinecone, qdrant.</t>
+          <t>Recommended for AI Engineer (7.3 years of experience). Top standout factors: (1) high rating on qualifications and skills screening and (2) excellent profile completeness and structured details. Core technical alignment includes: peft, pinecone, qdrant.</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Recommended for Senior Applied Scientist (5.4 years of experience). Top standout factors: (1) high BM25 search relevance matching and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: milvus, opensearch.</t>
+          <t>Recommended for Senior Applied Scientist (5.4 years of experience). Top standout factors: (1) highly relevant match with job description keywords and (2) strong matching keywords in resume text. Core technical alignment includes: milvus, opensearch.</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (4.6 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) proven familiarity with adjacent technology stacks, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, opensearch, peft, pinecone.</t>
+          <t>Recommended for Machine Learning Engineer (4.6 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) proven familiarity with related tech stacks and adjacent areas, and (3) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, opensearch, peft, pinecone.</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Recommended for ML Engineer (5.3 years of experience). Top standout factors: (1) high recruiter interest &amp; profile visibility. Core technical alignment includes: embeddings, milvus, opensearch, pinecone.</t>
+          <t>Recommended for ML Engineer (5.3 years of experience). Top standout factors: (1) high recruiter response rate and activity. Core technical alignment includes: embeddings, milvus, opensearch, pinecone.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (16.9 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) high BM25 search relevance matching. Core technical alignment includes: embeddings, faiss, milvus, opensearch.</t>
+          <t>Recommended for AI Engineer (16.9 years of experience). Top standout factors: (1) strong matching keywords in resume text and (2) highly relevant match with job description keywords. Core technical alignment includes: embeddings, faiss, milvus, opensearch.</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (6.8 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: elasticsearch, opensearch, qlora.</t>
+          <t>Recommended for NLP Engineer (6.8 years of experience). Top standout factors: (1) high rating on qualifications and skills screening. Core technical alignment includes: elasticsearch, opensearch, qlora.</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (6.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
+          <t>Recommended for Machine Learning Engineer (6.0 years of experience). Top standout factors: (1) strong matching keywords in resume text and (2) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (4.1 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) strong semantic concept alignment. Core technical alignment includes: milvus, opensearch, peft, python.</t>
+          <t>Recommended for Recommendation Systems Engineer (4.1 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas and (2) strong alignment with the core tech stack and domain. Core technical alignment includes: milvus, opensearch, peft, python.</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (4.9 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) broad Jaccard skills-set overlap. Core technical alignment includes: elasticsearch, embeddings, opensearch, python.</t>
+          <t>Recommended for AI Engineer (4.9 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas and (2) broad coverage of matching skills and related areas. Core technical alignment includes: elasticsearch, embeddings, opensearch, python.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Recommended for Staff Machine Learning Engineer (8.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) high BM25 search relevance matching, and (3) comprehensive profile completeness metrics. Core technical alignment includes: peft, python.</t>
+          <t>Recommended for Staff Machine Learning Engineer (8.0 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) highly relevant match with job description keywords, and (3) excellent profile completeness and structured details. Core technical alignment includes: peft, python.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (4.2 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) high BM25 search relevance matching, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, embeddings, opensearch, peft.</t>
+          <t>Recommended for Applied ML Engineer (4.2 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) highly relevant match with job description keywords, and (3) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, embeddings, opensearch, peft.</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Recommended for Applied ML Engineer (6.6 years of experience). Top standout factors: (1) proven familiarity with adjacent technology stacks and (2) broad Jaccard skills-set overlap. Core technical alignment includes: embeddings, lora, milvus, peft.</t>
+          <t>Recommended for Applied ML Engineer (6.6 years of experience). Top standout factors: (1) proven familiarity with related tech stacks and adjacent areas and (2) broad coverage of matching skills and related areas. Core technical alignment includes: embeddings, lora, milvus, peft.</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (16.1 years of experience). Top standout factors: (1) high recruiter interest &amp; profile visibility, (2) high BM25 search relevance matching, and (3) optimal TF-IDF keyword relevance score. Core technical alignment includes: embeddings, milvus, peft, qlora.</t>
+          <t>Recommended for NLP Engineer (16.1 years of experience). Top standout factors: (1) high recruiter response rate and activity, (2) highly relevant match with job description keywords, and (3) strong matching keywords in resume text. Core technical alignment includes: embeddings, milvus, peft, qlora.</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (6.5 years of experience). Top standout factors: (1) strong semantic concept alignment, (2) optimal TF-IDF keyword relevance score, and (3) high BM25 search relevance matching. Core technical alignment includes: elasticsearch, embeddings, opensearch, weaviate.</t>
+          <t>Recommended for Senior Data Scientist (6.5 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain, (2) strong matching keywords in resume text, and (3) highly relevant match with job description keywords. Core technical alignment includes: elasticsearch, embeddings, opensearch, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Recommended for AI Engineer (4.0 years of experience). Top standout factors: (1) broad Jaccard skills-set overlap and (2) proven familiarity with adjacent technology stacks. Core technical alignment includes: elasticsearch, faiss, milvus, peft.</t>
+          <t>Recommended for AI Engineer (4.0 years of experience). Top standout factors: (1) broad coverage of matching skills and related areas and (2) proven familiarity with related tech stacks and adjacent areas. Core technical alignment includes: elasticsearch, faiss, milvus, peft.</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (5.7 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) high BM25 search relevance matching. Core technical alignment includes: elasticsearch, opensearch, qdrant, weaviate.</t>
+          <t>Recommended for Machine Learning Engineer (5.7 years of experience). Top standout factors: (1) strong matching keywords in resume text and (2) highly relevant match with job description keywords. Core technical alignment includes: elasticsearch, opensearch, qdrant, weaviate.</t>
         </is>
       </c>
     </row>
@@ -1702,14 +1702,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (3.0 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score and (2) high BM25 search relevance matching. Core technical alignment includes: embeddings, peft, qdrant, weaviate.</t>
+          <t>Recommended for Search Engineer (3.0 years of experience). Top standout factors: (1) strong matching keywords in resume text and (2) highly relevant match with job description keywords. Core technical alignment includes: embeddings, peft, qdrant, weaviate.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CAND_0075439</t>
+          <t>CAND_0096172</t>
         </is>
       </c>
       <c r="B95">
@@ -1720,14 +1720,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (4.3 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
+          <t>Recommended for NLP Engineer (5.2 years of experience). Top standout factors: (1) high rating on qualifications and skills screening and (2) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CAND_0096172</t>
+          <t>CAND_0075439</t>
         </is>
       </c>
       <c r="B96">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Recommended for NLP Engineer (5.2 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening and (2) strong semantic concept alignment. Core technical alignment includes: elasticsearch, opensearch, python, qdrant.</t>
+          <t>Recommended for Machine Learning Engineer (4.3 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, embeddings, lora, opensearch.</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) strong semantic concept alignment. Core technical alignment includes: lora, opensearch, python, qlora.</t>
+          <t>Recommended for Recommendation Systems Engineer (6.5 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain. Core technical alignment includes: lora, opensearch, python, qlora.</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Recommended for Machine Learning Engineer (4.5 years of experience). Top standout factors: (1) optimal TF-IDF keyword relevance score, (2) top performance on rubric-based LLM screening, and (3) strong semantic concept alignment. Core technical alignment includes: elasticsearch, embeddings, python.</t>
+          <t>Recommended for Machine Learning Engineer (4.5 years of experience). Top standout factors: (1) strong matching keywords in resume text, (2) high rating on qualifications and skills screening, and (3) strong alignment with the core tech stack and domain. Core technical alignment includes: elasticsearch, embeddings, python.</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Recommended for Search Engineer (5.1 years of experience). Top standout factors: (1) strong semantic concept alignment and (2) optimal TF-IDF keyword relevance score. Core technical alignment includes: elasticsearch, qdrant, qlora.</t>
+          <t>Recommended for Search Engineer (5.1 years of experience). Top standout factors: (1) strong alignment with the core tech stack and domain and (2) strong matching keywords in resume text. Core technical alignment includes: elasticsearch, qdrant, qlora.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Recommended for Senior Data Scientist (7.0 years of experience). Top standout factors: (1) top performance on rubric-based LLM screening. Core technical alignment includes: faiss, milvus, qdrant.</t>
+          <t>Recommended for Senior Data Scientist (7.0 years of experience). Top standout factors: (1) high rating on qualifications and skills screening. Core technical alignment includes: faiss, milvus, qdrant.</t>
         </is>
       </c>
     </row>
